--- a/data/trans_bre/IP16B08-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16B08-Estudios-trans_bre.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 14,45</t>
+          <t>-8,8; 14,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 16,88</t>
+          <t>-8,89; 16,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,66</t>
+          <t>0,0; 61,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 167,77</t>
+          <t>0,0; 158,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 7,14</t>
+          <t>-17,01; 6,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,54</t>
+          <t>0,0; 22,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 7,62</t>
+          <t>-18,25; 7,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,12</t>
+          <t>0,0; 28,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">

--- a/data/trans_bre/IP16B08-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16B08-Estudios-trans_bre.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 14,36</t>
+          <t>-8,77; 14,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 16,88</t>
+          <t>-8,92; 16,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,36</t>
+          <t>0,0; 61,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 158,69</t>
+          <t>0,0; 161,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 6,93</t>
+          <t>-16,63; 7,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,1</t>
+          <t>0,0; 25,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 7,38</t>
+          <t>-17,07; 7,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,46</t>
+          <t>0,0; 34,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
